--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-signe-vital-observe.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-signe-vital-observe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -839,6 +839,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7989,7 +7993,7 @@
         <v>74</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>74</v>
@@ -7997,10 +8001,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8026,10 +8030,10 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8060,7 +8064,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8078,7 +8082,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8098,10 +8102,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8199,10 +8203,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8243,7 +8247,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8302,10 +8306,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8405,10 +8409,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8508,10 +8512,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8611,10 +8615,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8714,10 +8718,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8815,10 +8819,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8916,10 +8920,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9019,10 +9023,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9122,10 +9126,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9225,10 +9229,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9251,13 +9255,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9308,7 +9312,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9328,10 +9332,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9354,7 +9358,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9387,7 +9391,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9405,7 +9409,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9425,10 +9429,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9451,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9504,7 +9508,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9524,10 +9528,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9583,25 +9587,25 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9621,10 +9625,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9647,13 +9651,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9704,7 +9708,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9724,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9750,13 +9754,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9787,7 +9791,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -9805,7 +9809,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9825,10 +9829,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9851,13 +9855,13 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9888,7 +9892,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -9906,7 +9910,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9926,10 +9930,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9955,10 +9959,10 @@
         <v>177</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10009,7 +10013,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10029,10 +10033,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10055,7 +10059,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10108,7 +10112,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10128,10 +10132,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10154,7 +10158,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10207,7 +10211,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10227,10 +10231,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10253,7 +10257,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10306,7 +10310,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10326,10 +10330,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10352,13 +10356,13 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10409,7 +10413,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10429,10 +10433,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10455,7 +10459,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10508,7 +10512,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10528,10 +10532,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10554,7 +10558,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10607,7 +10611,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10627,10 +10631,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10653,7 +10657,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10706,7 +10710,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10726,10 +10730,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10752,7 +10756,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10805,7 +10809,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10825,10 +10829,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10851,7 +10855,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10904,7 +10908,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10924,10 +10928,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10950,7 +10954,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11003,7 +11007,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11023,10 +11027,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11049,11 +11053,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11104,7 +11108,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11124,10 +11128,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11225,10 +11229,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11326,10 +11330,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11427,10 +11431,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11528,10 +11532,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11631,10 +11635,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11734,10 +11738,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11837,10 +11841,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11940,10 +11944,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12041,10 +12045,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12078,7 +12082,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>74</v>
@@ -12100,7 +12104,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>74</v>
@@ -12118,7 +12122,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12138,10 +12142,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12164,7 +12168,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12217,7 +12221,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -12237,10 +12241,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12263,7 +12267,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12316,7 +12320,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
